--- a/conf/paramConfig.xlsx
+++ b/conf/paramConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asamuel/Projects/ccs-datim-data-import/conf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD35ABA-BAC5-7144-AF47-90590D3F5B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE184F79-EBC7-4E4B-87F7-050FBB517703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2360" yWindow="1200" windowWidth="36400" windowHeight="17320" xr2:uid="{4E933D9A-35E3-C745-AC08-A164B8EEBD08}"/>
+    <workbookView xWindow="2360" yWindow="1200" windowWidth="36400" windowHeight="17320" activeTab="6" xr2:uid="{4E933D9A-35E3-C745-AC08-A164B8EEBD08}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_datim_exchange_orgunits" sheetId="13" r:id="rId1"/>
@@ -13411,12 +13411,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>394</v>
       </c>
-      <c r="B2">
-        <v>81776</v>
+      <c r="B2" s="6">
+        <v>160451</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
